--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（Lob）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（Lob）参数校验测试用例.xlsx
@@ -82,20 +82,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>语法：db.collectionspace.collection.putLob(&lt;file path&gt;)
-file path：需要拥有文件的读权限。必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>putLob，file path指定的文件不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>写Lob失败，提示文件不存在，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>putLob，file path取值为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -123,10 +110,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>putLob，file path指定的文件没有读权限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，写lob，file path指定的文件没有读权限，如：
 db.testCL.testCL.putLob('/data/mylob')，其中sdbadmin用户对'/data/mylob'文件没有读权限
 2、检查执行结果</t>
@@ -139,18 +122,6 @@
   <si>
     <t>语法：db.collectionspace.collection.deleteLob(&lt;oid&gt;)
 oid存在，必填。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deleteLob，oid不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deleteLob，oid非lob的oid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>putLob，oid取值为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -177,6 +148,113 @@
   </si>
   <si>
     <t>删除失败，提示参数错误，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，oid不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取指定oid失败，提示指定的lob不存在，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getLob失败，提示参数错误，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，写lob，file path指定的文件不存在，如：
+db.testCL.testCL.putLob('/data/mylob')，其中'/data/mylob'文件不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getLob成功，文件不存在会生成新的lob文件；路径不存在会按指定的路径创建；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getLob失败，提示权限受限，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getLob失败，提示文件已存在，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，oid取值为空，如：
+db.testCL.testCL.getLob('5435e7b69487faa663000897','')
+db.testCL.testCL.getLob('5435e7b69487faa663000897',)
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，oid取值为空，如：
+db.testCL.testCL.getLob('','/data/newlob')
+db.testCL.testCL.getLob(,'/data/newlob')
+db.testCL.testCL.getLob()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件不存在，覆盖如下取值：
+   a.指定的文件不存在，如：db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob')，其中'/data/newlob'文件不存在
+   b.指定的路径不存在，如：db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob')，其中'/data'路径不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件没有可写权限，如：
+db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob')，其中sdbadmin用户对'/data/newlob'文件没有可写权限
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getLob成功，原文件被强制覆盖；检查lob获取正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件已存在，且forced:false，如：
+db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:false)，其中'/data/newlob'已存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件已存在，且forced:true，如：
+db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:true)，其中'/data/newlob'已存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，forced取值非法，其他参数正确，如：
+db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:test)，其中'/data/newlob'已存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，forced取值为空，如：
+db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:)
+db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',)
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.collection.listLobs()，无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，listLobs，指定查询条件查询，如：
+db.collectionspace.collection.listLobs('5435e7b69487faa663000897)
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询成功，查询条件被忽略，查询结果为所有的lobs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.collection.putLob(&lt;file path&gt;)
+file path：需要拥有文件的读权限。必填</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -189,146 +267,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getLob，oid不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，oid取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，oid不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取指定oid失败，提示指定的lob不存在，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob失败，提示参数错误，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，file path指定的文件不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，写lob，file path指定的文件不存在，如：
-db.testCL.testCL.putLob('/data/mylob')，其中'/data/mylob'文件不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob成功，文件不存在会生成新的lob文件；路径不存在会按指定的路径创建；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，file path指定的路径没有可写权限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob失败，提示权限受限，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob失败，提示文件已存在，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，file path取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，oid取值为空，如：
-db.testCL.testCL.getLob('5435e7b69487faa663000897','')
-db.testCL.testCL.getLob('5435e7b69487faa663000897',)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，oid取值为空，如：
-db.testCL.testCL.getLob('','/data/newlob')
-db.testCL.testCL.getLob(,'/data/newlob')
-db.testCL.testCL.getLob()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件不存在，覆盖如下取值：
-   a.指定的文件不存在，如：db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob')，其中'/data/newlob'文件不存在
-   b.指定的路径不存在，如：db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob')，其中'/data'路径不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件没有可写权限，如：
-db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob')，其中sdbadmin用户对'/data/newlob'文件没有可写权限
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob成功，原文件被强制覆盖；检查lob获取正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，file path指定的文件已存在,且forced:false</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，file path指定的文件已存在,且forced:true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件已存在，且forced:false，如：
-db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:false)，其中'/data/newlob'已存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，file path指定的文件已存在，且forced:true，如：
-db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:true)，其中'/data/newlob'已存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，forced取有非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getLob，forced取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，forced取值非法，其他参数正确，如：
-db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:test)，其中'/data/newlob'已存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，getLob，forced取值为空，如：
-db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',forced:)
-db.testCL.testCL.getLob('5435e7b69487faa663000897','/data/newlob',)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.collectionspace.collection.listLobs()，无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listLobs，指定查询条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户登录sequoiadb服务器，进入sdb，listLobs，指定查询条件查询，如：
-db.collectionspace.collection.listLobs('5435e7b69487faa663000897)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询成功，查询条件被忽略，查询结果为所有的lobs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>putLob，file path指定的文件不存在_st.verify.lob.001</t>
+  </si>
+  <si>
+    <t>putLob，file path指定的文件没有读权限_st.verify.lob.002</t>
+  </si>
+  <si>
+    <t>putLob，file path取值为空_st.verify.lob.003</t>
+  </si>
+  <si>
+    <t>deleteLob，oid不存在_st.verify.lob.004</t>
+  </si>
+  <si>
+    <t>deleteLob，oid非lob的oid_st.verify.lob.005</t>
+  </si>
+  <si>
+    <t>deleteLob，oid取值为空_st.verify.lob.006</t>
+  </si>
+  <si>
+    <t>getLob，oid不存在_st.verify.lob.007</t>
+  </si>
+  <si>
+    <t>getLob，oid取值为空_st.verify.lob.008</t>
+  </si>
+  <si>
+    <t>getLob，file path指定的文件不存在_st.verify.lob.009</t>
+  </si>
+  <si>
+    <t>getLob，file path指定的路径没有可写权限_st.verify.lob.010</t>
+  </si>
+  <si>
+    <t>getLob，file path取值为空_st.verify.lob.011</t>
+  </si>
+  <si>
+    <t>getLob，file path指定的文件已存在,且forced:false_st.verify.lob.012</t>
+  </si>
+  <si>
+    <t>getLob，file path指定的文件已存在,且forced:true_st.verify.lob.013</t>
+  </si>
+  <si>
+    <t>getLob，forced取有非法_st.verify.lob.014</t>
+  </si>
+  <si>
+    <t>getLob，forced取值为空_st.verify.lob.015</t>
+  </si>
+  <si>
+    <t>listLobs，指定查询条件查询_st.verify.lob.016</t>
   </si>
 </sst>
 </file>
@@ -806,7 +790,7 @@
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -870,13 +854,13 @@
     </row>
     <row r="3" spans="1:9" ht="94.5">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -888,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -899,282 +883,402 @@
     </row>
     <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="94.5">
       <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="94.5">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="94.5">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="189">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="94.5">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="162">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="94.5">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="94.5">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="94.5">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="94.5">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="94.5">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="94.5">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="94.5">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
       <c r="G18" s="2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2"/>
